--- a/rules/CORE-000580/negative/03/data/unit-test-coreid-CG0325-negative03.xlsx
+++ b/rules/CORE-000580/negative/03/data/unit-test-coreid-CG0325-negative03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000580\negative\03\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63D1721-D8A9-4D27-B472-1603927ACDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175B150F-820D-4AA1-9C16-445CC547D6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="52">
   <si>
     <t>Product</t>
   </si>
@@ -173,6 +173,12 @@
   </si>
   <si>
     <t>[ABSENT]</t>
+  </si>
+  <si>
+    <t>E005</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -260,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -279,10 +285,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -637,7 +646,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -861,304 +870,13 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12">
-        <v>10</v>
-      </c>
-      <c r="E12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13">
-        <v>10</v>
-      </c>
-      <c r="E13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14">
-        <v>10</v>
-      </c>
-      <c r="E14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>3</v>
-      </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15">
-        <v>10</v>
-      </c>
-      <c r="E15" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>3</v>
-      </c>
-      <c r="B16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16">
-        <v>10</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>4</v>
-      </c>
-      <c r="B17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17">
-        <v>11</v>
-      </c>
-      <c r="E17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>4</v>
-      </c>
-      <c r="B18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18">
-        <v>11</v>
-      </c>
-      <c r="E18" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19">
-        <v>11</v>
-      </c>
-      <c r="E19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>4</v>
-      </c>
-      <c r="B20" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20">
-        <v>11</v>
-      </c>
-      <c r="E20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>4</v>
-      </c>
-      <c r="B21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21">
-        <v>11</v>
-      </c>
-      <c r="E21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>5</v>
-      </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22">
-        <v>12</v>
-      </c>
-      <c r="E22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>5</v>
-      </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23">
-        <v>12</v>
-      </c>
-      <c r="E23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>5</v>
-      </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24">
-        <v>12</v>
-      </c>
-      <c r="E24" t="s">
-        <v>18</v>
-      </c>
-      <c r="F24" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>5</v>
-      </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25">
-        <v>12</v>
-      </c>
-      <c r="E25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>5</v>
-      </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26">
-        <v>12</v>
-      </c>
-      <c r="E26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" t="s">
-        <v>45</v>
-      </c>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F17" s="8"/>
+    </row>
+    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F22" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1168,7 +886,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="17.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
@@ -1193,7 +911,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>20</v>
       </c>
@@ -1262,7 +980,7 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>27</v>
       </c>
@@ -1282,7 +1000,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>27</v>
       </c>
@@ -1302,7 +1020,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
@@ -1322,7 +1040,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>27</v>
       </c>
@@ -1342,7 +1060,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>27</v>
       </c>
@@ -1362,64 +1080,64 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="8" t="s">
+      <c r="C10" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="8" t="s">
+      <c r="E10" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>45</v>
+      <c r="F12" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
